--- a/Marine_Incident_Dataset.xlsx
+++ b/Marine_Incident_Dataset.xlsx
@@ -15,13 +15,13 @@
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="404">
   <si>
     <t>Date of occurrence</t>
   </si>
@@ -1211,10 +1211,28 @@
     <t>oil and gas water point</t>
   </si>
   <si>
-    <t>Strong wind</t>
-  </si>
-  <si>
     <t>Strong wind, Heavy tides</t>
+  </si>
+  <si>
+    <t>L.Nyaguo</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>Boat capsizing due to bad weather</t>
+  </si>
+  <si>
+    <t>Non use of life jacket</t>
+  </si>
+  <si>
+    <t>Non use of life jacket, No supervision</t>
+  </si>
+  <si>
+    <t>Night-time fishing operations</t>
+  </si>
+  <si>
+    <t>Outboard engine yamaha 2 stroke</t>
   </si>
 </sst>
 </file>
@@ -1687,7 +1705,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" dataField="1" showAll="0">
@@ -2256,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T139"/>
+  <dimension ref="A1:T144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
@@ -8538,16 +8556,194 @@
         <v>395</v>
       </c>
       <c r="J139" t="s">
+        <v>399</v>
+      </c>
+      <c r="K139" t="s">
         <v>396</v>
-      </c>
-      <c r="K139" t="s">
-        <v>397</v>
       </c>
       <c r="L139" t="s">
         <v>7</v>
       </c>
       <c r="M139">
         <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="2:20" ht="15.75">
+      <c r="B140" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C140" s="11">
+        <v>46054</v>
+      </c>
+      <c r="F140" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="J140" t="s">
+        <v>399</v>
+      </c>
+      <c r="K140" t="s">
+        <v>400</v>
+      </c>
+      <c r="L140" t="s">
+        <v>7</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>1</v>
+      </c>
+      <c r="P140">
+        <v>1</v>
+      </c>
+      <c r="T140" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="141" spans="2:20" ht="15.75">
+      <c r="B141" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C141" s="11">
+        <v>46054</v>
+      </c>
+      <c r="F141" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="J141" t="s">
+        <v>260</v>
+      </c>
+      <c r="K141" t="s">
+        <v>401</v>
+      </c>
+      <c r="L141" t="s">
+        <v>261</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="P141">
+        <v>1</v>
+      </c>
+      <c r="T141" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="142" spans="2:20" ht="15.75">
+      <c r="B142" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C142" s="11">
+        <v>46054</v>
+      </c>
+      <c r="F142" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="J142" t="s">
+        <v>260</v>
+      </c>
+      <c r="L142" t="s">
+        <v>261</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>1</v>
+      </c>
+      <c r="P142">
+        <v>1</v>
+      </c>
+      <c r="T142" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="143" spans="2:20" ht="15.75">
+      <c r="B143" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C143" s="11">
+        <v>46065</v>
+      </c>
+      <c r="D143" s="15">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="E143" s="7">
+        <v>46066</v>
+      </c>
+      <c r="F143" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G143" t="s">
+        <v>111</v>
+      </c>
+      <c r="H143" t="s">
+        <v>252</v>
+      </c>
+      <c r="I143" t="s">
+        <v>393</v>
+      </c>
+      <c r="J143" t="s">
+        <v>367</v>
+      </c>
+      <c r="K143" t="s">
+        <v>402</v>
+      </c>
+      <c r="L143" t="s">
+        <v>7</v>
+      </c>
+      <c r="M143">
+        <v>1</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>403</v>
+      </c>
+      <c r="T143" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="144" spans="2:20" ht="15.75">
+      <c r="B144" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C144" s="11">
+        <v>46065</v>
+      </c>
+      <c r="D144" s="15">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="E144" s="7">
+        <v>46066</v>
+      </c>
+      <c r="F144" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G144" t="s">
+        <v>111</v>
+      </c>
+      <c r="H144" t="s">
+        <v>252</v>
+      </c>
+      <c r="I144" t="s">
+        <v>393</v>
+      </c>
+      <c r="J144" t="s">
+        <v>367</v>
+      </c>
+      <c r="L144" t="s">
+        <v>402</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>403</v>
+      </c>
+      <c r="T144" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>

--- a/Marine_Incident_Dataset.xlsx
+++ b/Marine_Incident_Dataset.xlsx
@@ -9,19 +9,24 @@
   <sheets>
     <sheet name="Sheet9" sheetId="9" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet5" sheetId="13" r:id="rId3"/>
+    <sheet name="Sheet6" sheetId="14" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="11" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$2:$T$128</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId6"/>
+    <pivotCache cacheId="14" r:id="rId7"/>
+    <pivotCache cacheId="19" r:id="rId8"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="430">
   <si>
     <t>Date of occurrence</t>
   </si>
@@ -1233,6 +1238,84 @@
   </si>
   <si>
     <t>Outboard engine yamaha 2 stroke</t>
+  </si>
+  <si>
+    <t>Searching for sailing boat</t>
+  </si>
+  <si>
+    <t>Fatal crocodile attack</t>
+  </si>
+  <si>
+    <t>Kamwanga</t>
+  </si>
+  <si>
+    <t>Crocodile attack</t>
+  </si>
+  <si>
+    <t>Bathing at the shoreline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bathing at the shoreline </t>
+  </si>
+  <si>
+    <t>11/18/02/2026</t>
+  </si>
+  <si>
+    <t>Lolwe police station</t>
+  </si>
+  <si>
+    <t>Suicide</t>
+  </si>
+  <si>
+    <t>KK beach</t>
+  </si>
+  <si>
+    <t>Boat instability due to imbalance</t>
+  </si>
+  <si>
+    <t>Small boat size</t>
+  </si>
+  <si>
+    <t>Kigo Marine detach</t>
+  </si>
+  <si>
+    <t>R.Nyagak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatal accident(vehicle plunged river) </t>
+  </si>
+  <si>
+    <t>Suicide by drowning</t>
+  </si>
+  <si>
+    <t>suicide by drowning</t>
+  </si>
+  <si>
+    <t>Fishing in isolated areas</t>
+  </si>
+  <si>
+    <t>Outboard engine</t>
+  </si>
+  <si>
+    <t>Kasensero detach</t>
+  </si>
+  <si>
+    <t>Accidental loss of property</t>
+  </si>
+  <si>
+    <t>Febraury/2026</t>
+  </si>
+  <si>
+    <t>Pond</t>
+  </si>
+  <si>
+    <t>Water pump</t>
+  </si>
+  <si>
+    <t>Nkese</t>
+  </si>
+  <si>
+    <t>Strong winds</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1385,6 +1468,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1426,6 +1512,215 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="KAGIMU MOSES" refreshedDate="46083.372777083336" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="21">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:S22" sheet="Sheet3"/>
+  </cacheSource>
+  <cacheFields count="19">
+    <cacheField name="INCIDENT" numFmtId="0">
+      <sharedItems count="8">
+        <s v="Aggravated Robbery"/>
+        <s v="Drowning"/>
+        <s v="Fatal Vessel collision "/>
+        <s v="Boat capsizing"/>
+        <s v="Robbery"/>
+        <s v="Fatal crocodile attack"/>
+        <s v="Suicide by drowning"/>
+        <s v="Fatal accident(vehicle plunged river) "/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Date of occurrence" numFmtId="165">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-01T00:00:00" maxDate="2026-02-27T00:00:00" count="14">
+        <d v="2026-01-01T00:00:00"/>
+        <d v="2026-01-10T00:00:00"/>
+        <d v="2026-01-28T00:00:00"/>
+        <d v="2026-01-16T00:00:00"/>
+        <d v="2026-02-05T00:00:00"/>
+        <d v="2026-02-01T00:00:00"/>
+        <d v="2026-02-12T00:00:00"/>
+        <d v="2026-02-16T00:00:00"/>
+        <d v="2026-02-18T00:00:00"/>
+        <d v="2026-02-21T00:00:00"/>
+        <d v="2026-02-23T00:00:00"/>
+        <d v="2026-02-24T00:00:00"/>
+        <d v="2026-02-19T00:00:00"/>
+        <d v="2026-02-26T00:00:00"/>
+      </sharedItems>
+      <fieldGroup base="1">
+        <rangePr groupBy="months" startDate="2026-01-01T00:00:00" endDate="2026-02-27T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;1/1/2026"/>
+          <s v="Jan"/>
+          <s v="Feb"/>
+          <s v="Mar"/>
+          <s v="Apr"/>
+          <s v="May"/>
+          <s v="Jun"/>
+          <s v="Jul"/>
+          <s v="Aug"/>
+          <s v="Sep"/>
+          <s v="Oct"/>
+          <s v="Nov"/>
+          <s v="Dec"/>
+          <s v="&gt;2/27/2026"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Time of occurrence" numFmtId="0">
+      <sharedItems containsDate="1" containsBlank="1" containsMixedTypes="1" minDate="1899-12-30T01:00:00" maxDate="1899-12-30T23:00:00"/>
+    </cacheField>
+    <cacheField name="Date of reporting" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-01-01T00:00:00" maxDate="2026-02-28T00:00:00"/>
+    </cacheField>
+    <cacheField name="Water body" numFmtId="0">
+      <sharedItems count="5">
+        <s v="L.Victoria"/>
+        <s v="L.Albert"/>
+        <s v="L.Nyaguo"/>
+        <s v="Swimming pool"/>
+        <s v="R.Nyagak"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Zone" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Detach" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Place of occurrence" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Primary Cause of Incident" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Contributing Factors" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Activity before the Incident" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Number of Crews" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="14"/>
+    </cacheField>
+    <cacheField name="number of fatalities" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="6"/>
+    </cacheField>
+    <cacheField name="number of persons rescued" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="8"/>
+    </cacheField>
+    <cacheField name="number of body retrievals" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="6"/>
+    </cacheField>
+    <cacheField name="Property lost/damaged " numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Value of property lost/damaged" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="SDREF/Police station" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Action taken" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="KAGIMU MOSES" refreshedDate="46083.394237731482" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="22">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:S23" sheet="Sheet3"/>
+  </cacheSource>
+  <cacheFields count="19">
+    <cacheField name="INCIDENT" numFmtId="0">
+      <sharedItems count="9">
+        <s v="Aggravated Robbery"/>
+        <s v="Drowning"/>
+        <s v="Fatal Vessel collision "/>
+        <s v="Boat capsizing"/>
+        <s v="Robbery"/>
+        <s v="Fatal crocodile attack"/>
+        <s v="Suicide by drowning"/>
+        <s v="Fatal accident(vehicle plunged river) "/>
+        <s v="Accidental loss of property"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Date of occurrence" numFmtId="165">
+      <sharedItems containsDate="1" containsMixedTypes="1" minDate="2026-01-01T00:00:00" maxDate="2026-02-27T00:00:00" count="15">
+        <d v="2026-01-01T00:00:00"/>
+        <d v="2026-01-10T00:00:00"/>
+        <d v="2026-01-28T00:00:00"/>
+        <d v="2026-01-16T00:00:00"/>
+        <d v="2026-02-05T00:00:00"/>
+        <d v="2026-02-01T00:00:00"/>
+        <d v="2026-02-12T00:00:00"/>
+        <d v="2026-02-16T00:00:00"/>
+        <d v="2026-02-18T00:00:00"/>
+        <d v="2026-02-21T00:00:00"/>
+        <d v="2026-02-23T00:00:00"/>
+        <d v="2026-02-24T00:00:00"/>
+        <d v="2026-02-19T00:00:00"/>
+        <d v="2026-02-26T00:00:00"/>
+        <s v="Febraury/2026"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Time of occurrence" numFmtId="0">
+      <sharedItems containsDate="1" containsBlank="1" containsMixedTypes="1" minDate="1899-12-30T01:00:00" maxDate="1899-12-30T23:00:00"/>
+    </cacheField>
+    <cacheField name="Date of reporting" numFmtId="0">
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-01-01T00:00:00" maxDate="2026-02-28T00:00:00"/>
+    </cacheField>
+    <cacheField name="Water body" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Zone" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Detach" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Place of occurrence" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Primary Cause of Incident" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Contributing Factors" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Activity before the Incident" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Number of Crews" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="14"/>
+    </cacheField>
+    <cacheField name="number of fatalities" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="6"/>
+    </cacheField>
+    <cacheField name="number of persons rescued" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="8"/>
+    </cacheField>
+    <cacheField name="number of body retrievals" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="6"/>
+    </cacheField>
+    <cacheField name="Property lost/damaged " numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Value of property lost/damaged" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="SDREF/Police station" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Action taken" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="91">
   <r>
@@ -1700,6 +1995,919 @@
   </r>
   <r>
     <x v="7"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="21">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-01T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria northeast"/>
+    <s v="Samba"/>
+    <s v="Luwero"/>
+    <s v="Outright criminality"/>
+    <m/>
+    <s v="Fishing"/>
+    <n v="3"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Fuel, Fuel tank, Fuel line, clothes, Cash 200000/=, Torch worth 80000/="/>
+    <m/>
+    <s v="05/01/01/2026"/>
+    <s v="Lyabana police station"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <d v="2026-01-10T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria north"/>
+    <s v="Kigo"/>
+    <s v="Bulebi"/>
+    <s v="Net Entanglement"/>
+    <s v="Wearing buttoned shirt, Non use of life jacket"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <s v="04/10/01/2026"/>
+    <s v="Mponge police station"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-28T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Bumeru"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations, Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke 15HP"/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-28T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Bumeru"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations, Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke 15HP"/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <d v="1899-12-30T23:00:00"/>
+    <d v="2026-01-16T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria southwest"/>
+    <s v="Kasenyi"/>
+    <s v="Kiziru"/>
+    <s v="Ship collided with anchored fishing boat"/>
+    <s v="Night-time fishing operations, Poor visibility, Anchored in navigation channel, Non use of life jacket, Occupants asleep at the time of collision"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <s v="DEF 01/2026"/>
+    <s v="Kigungu police station"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-28T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Biisa"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations, Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke 15HP"/>
+    <m/>
+    <m/>
+    <s v="Bumeru police station"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-28T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Biisa"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations, Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke 15HP"/>
+    <m/>
+    <m/>
+    <s v="Bumeru police station"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <d v="1899-12-30T17:30:00"/>
+    <d v="2026-02-05T00:00:00"/>
+    <x v="1"/>
+    <s v="Albertine"/>
+    <s v="Panyimur"/>
+    <s v="oil and gas water point"/>
+    <s v="Boat capsizing due to bad weather"/>
+    <s v="Strong wind, Heavy tides"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <m/>
+    <m/>
+    <x v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Boat capsizing due to bad weather"/>
+    <s v="Non use of life jacket"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Media"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <m/>
+    <m/>
+    <x v="3"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Inability to swim"/>
+    <s v="Non use of life jacket, No supervision"/>
+    <s v="Swimming"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Media"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <m/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Inability to swim"/>
+    <m/>
+    <s v="Swimming"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Media"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <d v="1899-12-30T23:00:00"/>
+    <d v="2026-02-13T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Biisa"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke"/>
+    <m/>
+    <m/>
+    <s v="Sigulu marine detach"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <d v="1899-12-30T23:00:00"/>
+    <d v="2026-02-13T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Biisa"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke"/>
+    <m/>
+    <m/>
+    <s v="Sigulu marine detach"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <d v="1899-12-30T16:00:00"/>
+    <d v="2026-02-16T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria south"/>
+    <s v="Nkose"/>
+    <s v="Nkose"/>
+    <s v="unknown"/>
+    <s v="Non use of life jacket"/>
+    <s v="Searching for sailing boat"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="8"/>
+    <m/>
+    <d v="2026-02-18T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria southeast"/>
+    <s v="Lolwe"/>
+    <s v="Kamwanga"/>
+    <s v="Crocodile attack"/>
+    <s v="Bathing at the shoreline"/>
+    <s v="Bathing at the shoreline "/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <s v="11/18/02/2026"/>
+    <s v="Lolwe police station"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="8"/>
+    <m/>
+    <d v="2026-02-19T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria north"/>
+    <s v="Gaba"/>
+    <s v="Gaba"/>
+    <s v="Suicide"/>
+    <s v="Human error"/>
+    <s v="unknown"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <s v="unknown"/>
+    <d v="2026-02-21T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria north"/>
+    <m/>
+    <s v="KK beach"/>
+    <s v="unknown"/>
+    <s v="Non use of life jacket"/>
+    <s v="unknown"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Mpata police station"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="10"/>
+    <d v="1899-12-30T10:00:00"/>
+    <d v="2026-02-23T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria north"/>
+    <s v="Kigo"/>
+    <s v="Kigo"/>
+    <s v="Boat instability due to imbalance"/>
+    <s v="Small boat size"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Kigo Marine detach"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="11"/>
+    <m/>
+    <d v="2026-02-24T00:00:00"/>
+    <x v="4"/>
+    <s v="Albertine"/>
+    <s v="Panyimur"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="14"/>
+    <n v="6"/>
+    <n v="8"/>
+    <n v="6"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="12"/>
+    <d v="1899-12-30T07:30:00"/>
+    <d v="2026-02-19T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria east"/>
+    <s v="Jinja"/>
+    <s v="Jinja"/>
+    <s v="Suicide"/>
+    <m/>
+    <m/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <d v="1899-12-30T18:00:00"/>
+    <d v="2026-02-27T00:00:00"/>
+    <x v="0"/>
+    <s v="Victoria south"/>
+    <s v="Kasensero"/>
+    <s v="Lujabwa"/>
+    <s v="Outright criminality"/>
+    <s v="Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine"/>
+    <m/>
+    <m/>
+    <s v="Kasensero detach"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="22">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-01T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria northeast"/>
+    <s v="Samba"/>
+    <s v="Luwero"/>
+    <s v="Outright criminality"/>
+    <m/>
+    <s v="Fishing"/>
+    <n v="3"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Fuel, Fuel tank, Fuel line, clothes, Cash 200000/=, Torch worth 80000/="/>
+    <m/>
+    <s v="05/01/01/2026"/>
+    <s v="Lyabana police station"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <d v="2026-01-10T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria north"/>
+    <s v="Kigo"/>
+    <s v="Bulebi"/>
+    <s v="Net Entanglement"/>
+    <s v="Wearing buttoned shirt, Non use of life jacket"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <s v="04/10/01/2026"/>
+    <s v="Mponge police station"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-28T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Bumeru"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations, Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke 15HP"/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-28T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Bumeru"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations, Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke 15HP"/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <d v="1899-12-30T23:00:00"/>
+    <d v="2026-01-16T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria southwest"/>
+    <s v="Kasenyi"/>
+    <s v="Kiziru"/>
+    <s v="Ship collided with anchored fishing boat"/>
+    <s v="Night-time fishing operations, Poor visibility, Anchored in navigation channel, Non use of life jacket, Occupants asleep at the time of collision"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <s v="DEF 01/2026"/>
+    <s v="Kigungu police station"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-28T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Biisa"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations, Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke 15HP"/>
+    <m/>
+    <m/>
+    <s v="Bumeru police station"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <d v="1899-12-30T01:00:00"/>
+    <d v="2026-01-28T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Biisa"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations, Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke 15HP"/>
+    <m/>
+    <m/>
+    <s v="Bumeru police station"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <d v="1899-12-30T17:30:00"/>
+    <d v="2026-02-05T00:00:00"/>
+    <s v="L.Albert"/>
+    <s v="Albertine"/>
+    <s v="Panyimur"/>
+    <s v="oil and gas water point"/>
+    <s v="Boat capsizing due to bad weather"/>
+    <s v="Strong wind, Heavy tides"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <m/>
+    <m/>
+    <s v="L.Nyaguo"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Boat capsizing due to bad weather"/>
+    <s v="Non use of life jacket"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Media"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <m/>
+    <m/>
+    <s v="Swimming pool"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Inability to swim"/>
+    <s v="Non use of life jacket, No supervision"/>
+    <s v="Swimming"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Media"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="5"/>
+    <m/>
+    <m/>
+    <s v="L.Victoria"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Inability to swim"/>
+    <m/>
+    <s v="Swimming"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Media"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <d v="1899-12-30T23:00:00"/>
+    <d v="2026-02-13T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Biisa"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke"/>
+    <m/>
+    <m/>
+    <s v="Sigulu marine detach"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <d v="1899-12-30T23:00:00"/>
+    <d v="2026-02-13T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria southeast"/>
+    <s v="Sigulu"/>
+    <s v="Biisa"/>
+    <s v="Outright criminality"/>
+    <s v="Night-time fishing operations"/>
+    <s v="Fishing"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine yamaha 2 stroke"/>
+    <m/>
+    <m/>
+    <s v="Sigulu marine detach"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="7"/>
+    <d v="1899-12-30T16:00:00"/>
+    <d v="2026-02-16T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria south"/>
+    <s v="Nkose"/>
+    <s v="Nkose"/>
+    <s v="unknown"/>
+    <s v="Non use of life jacket"/>
+    <s v="Searching for sailing boat"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="8"/>
+    <m/>
+    <d v="2026-02-18T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria southeast"/>
+    <s v="Lolwe"/>
+    <s v="Kamwanga"/>
+    <s v="Crocodile attack"/>
+    <s v="Bathing at the shoreline"/>
+    <s v="Bathing at the shoreline "/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <s v="11/18/02/2026"/>
+    <s v="Lolwe police station"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="8"/>
+    <m/>
+    <d v="2026-02-19T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria north"/>
+    <s v="Gaba"/>
+    <s v="Gaba"/>
+    <s v="Suicide"/>
+    <s v="Human error"/>
+    <s v="unknown"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="9"/>
+    <s v="unknown"/>
+    <d v="2026-02-21T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria north"/>
+    <m/>
+    <s v="KK beach"/>
+    <s v="unknown"/>
+    <s v="Non use of life jacket"/>
+    <s v="unknown"/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Mpata police station"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="10"/>
+    <d v="1899-12-30T10:00:00"/>
+    <d v="2026-02-23T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria north"/>
+    <s v="Kigo"/>
+    <s v="Kigo"/>
+    <s v="Boat instability due to imbalance"/>
+    <s v="Small boat size"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Kigo Marine detach"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="11"/>
+    <m/>
+    <d v="2026-02-24T00:00:00"/>
+    <s v="R.Nyagak"/>
+    <s v="Albertine"/>
+    <s v="Panyimur"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="14"/>
+    <n v="6"/>
+    <n v="8"/>
+    <n v="6"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="12"/>
+    <d v="1899-12-30T07:30:00"/>
+    <d v="2026-02-19T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria east"/>
+    <s v="Jinja"/>
+    <s v="Jinja"/>
+    <s v="Suicide"/>
+    <m/>
+    <m/>
+    <n v="1"/>
+    <n v="1"/>
+    <m/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="13"/>
+    <d v="1899-12-30T18:00:00"/>
+    <d v="2026-02-27T00:00:00"/>
+    <s v="L.Victoria"/>
+    <s v="Victoria south"/>
+    <s v="Kasensero"/>
+    <s v="Lujabwa"/>
+    <s v="Outright criminality"/>
+    <s v="Fishing in isolated areas"/>
+    <s v="Fishing"/>
+    <n v="2"/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Outboard engine"/>
+    <m/>
+    <m/>
+    <s v="Kasensero detach"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="14"/>
+    <m/>
+    <m/>
+    <s v="Pond"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <s v="Water pump"/>
+    <m/>
+    <m/>
+    <m/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -1797,6 +3005,221 @@
     <dataField name="Count of INCIDENT" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable3" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField dataField="1" showAll="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="165" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of INCIDENT" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight10" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable4" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField dataField="1" showAll="0">
+      <items count="10">
+        <item x="8"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="14"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="12"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of INCIDENT" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight10" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
 </pivotTableDefinition>
 </file>
 
@@ -2274,7 +3697,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T144"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:T154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
@@ -2364,7 +3788,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.75">
+    <row r="3" spans="1:20" ht="15.75" hidden="1">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -2413,7 +3837,7 @@
       </c>
       <c r="T3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75">
+    <row r="4" spans="1:20" ht="15.75" hidden="1">
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2460,7 +3884,7 @@
       </c>
       <c r="T4" s="1"/>
     </row>
-    <row r="5" spans="1:20" ht="15.75">
+    <row r="5" spans="1:20" ht="15.75" hidden="1">
       <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2497,7 +3921,7 @@
       </c>
       <c r="T5" s="1"/>
     </row>
-    <row r="6" spans="1:20" ht="15.75">
+    <row r="6" spans="1:20" ht="15.75" hidden="1">
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
@@ -2546,7 +3970,7 @@
       </c>
       <c r="T6" s="1"/>
     </row>
-    <row r="7" spans="1:20" ht="15.75">
+    <row r="7" spans="1:20" ht="15.75" hidden="1">
       <c r="B7" s="1" t="s">
         <v>3</v>
       </c>
@@ -2595,7 +4019,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.75">
+    <row r="8" spans="1:20" ht="15.75" hidden="1">
       <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
@@ -2646,7 +4070,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.75">
+    <row r="9" spans="1:20" ht="15.75" hidden="1">
       <c r="B9" s="1" t="s">
         <v>3</v>
       </c>
@@ -2677,7 +4101,7 @@
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="1:20" ht="15.75">
+    <row r="10" spans="1:20" ht="15.75" hidden="1">
       <c r="B10" s="1" t="s">
         <v>36</v>
       </c>
@@ -2712,7 +4136,7 @@
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
     </row>
-    <row r="11" spans="1:20" ht="15.75">
+    <row r="11" spans="1:20" ht="15.75" hidden="1">
       <c r="B11" s="1" t="s">
         <v>3</v>
       </c>
@@ -2751,7 +4175,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.75">
+    <row r="12" spans="1:20" ht="15.75" hidden="1">
       <c r="B12" s="1" t="s">
         <v>45</v>
       </c>
@@ -2804,7 +4228,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.75">
+    <row r="13" spans="1:20" ht="15.75" hidden="1">
       <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
@@ -2843,7 +4267,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.75">
+    <row r="14" spans="1:20" ht="15.75" hidden="1">
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -2882,7 +4306,7 @@
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
     </row>
-    <row r="15" spans="1:20" ht="15.75">
+    <row r="15" spans="1:20" ht="15.75" hidden="1">
       <c r="B15" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,7 +4349,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.75">
+    <row r="16" spans="1:20" ht="15.75" hidden="1">
       <c r="B16" s="1" t="s">
         <v>44</v>
       </c>
@@ -2968,7 +4392,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="2:20" ht="15.75">
+    <row r="17" spans="2:20" ht="15.75" hidden="1">
       <c r="B17" s="1" t="s">
         <v>60</v>
       </c>
@@ -3011,7 +4435,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="2:20" ht="15.75">
+    <row r="18" spans="2:20" ht="15.75" hidden="1">
       <c r="B18" s="1" t="s">
         <v>3</v>
       </c>
@@ -3058,7 +4482,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="2:20" ht="15.75">
+    <row r="19" spans="2:20" ht="15.75" hidden="1">
       <c r="B19" s="1" t="s">
         <v>3</v>
       </c>
@@ -3103,7 +4527,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="2:20" ht="15.75">
+    <row r="20" spans="2:20" ht="15.75" hidden="1">
       <c r="B20" s="1" t="s">
         <v>3</v>
       </c>
@@ -3144,7 +4568,7 @@
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
     </row>
-    <row r="21" spans="2:20" ht="15.75">
+    <row r="21" spans="2:20" ht="15.75" hidden="1">
       <c r="B21" s="1" t="s">
         <v>3</v>
       </c>
@@ -3189,7 +4613,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:20" ht="15.75">
+    <row r="22" spans="2:20" ht="15.75" hidden="1">
       <c r="B22" s="1" t="s">
         <v>60</v>
       </c>
@@ -3234,7 +4658,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="2:20" ht="15.75">
+    <row r="23" spans="2:20" ht="15.75" hidden="1">
       <c r="B23" s="1" t="s">
         <v>73</v>
       </c>
@@ -3279,7 +4703,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="2:20" ht="15.75">
+    <row r="24" spans="2:20" ht="15.75" hidden="1">
       <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
@@ -3326,7 +4750,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="2:20" ht="15.75">
+    <row r="25" spans="2:20" ht="15.75" hidden="1">
       <c r="B25" s="1" t="s">
         <v>44</v>
       </c>
@@ -3373,7 +4797,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="2:20" ht="15.75">
+    <row r="26" spans="2:20" ht="15.75" hidden="1">
       <c r="B26" s="1" t="s">
         <v>44</v>
       </c>
@@ -3418,7 +4842,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="2:20" ht="15.75">
+    <row r="27" spans="2:20" ht="15.75" hidden="1">
       <c r="B27" s="1" t="s">
         <v>3</v>
       </c>
@@ -3463,7 +4887,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="2:20" ht="15.75">
+    <row r="28" spans="2:20" ht="15.75" hidden="1">
       <c r="B28" s="1" t="s">
         <v>44</v>
       </c>
@@ -3510,7 +4934,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="2:20" ht="15.75">
+    <row r="29" spans="2:20" ht="15.75" hidden="1">
       <c r="B29" s="1" t="s">
         <v>3</v>
       </c>
@@ -3551,7 +4975,7 @@
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
     </row>
-    <row r="30" spans="2:20" ht="15.75">
+    <row r="30" spans="2:20" ht="15.75" hidden="1">
       <c r="B30" s="1" t="s">
         <v>3</v>
       </c>
@@ -3600,7 +5024,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="2:20" ht="15.75">
+    <row r="31" spans="2:20" ht="15.75" hidden="1">
       <c r="B31" s="1" t="s">
         <v>104</v>
       </c>
@@ -3649,7 +5073,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="2:20" ht="15.75">
+    <row r="32" spans="2:20" ht="15.75" hidden="1">
       <c r="B32" s="1" t="s">
         <v>3</v>
       </c>
@@ -3694,7 +5118,7 @@
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
     </row>
-    <row r="33" spans="2:20" ht="15.75">
+    <row r="33" spans="2:20" ht="15.75" hidden="1">
       <c r="B33" s="1" t="s">
         <v>110</v>
       </c>
@@ -3739,7 +5163,7 @@
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
     </row>
-    <row r="34" spans="2:20" ht="15.75">
+    <row r="34" spans="2:20" ht="15.75" hidden="1">
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
@@ -3790,7 +5214,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="2:20" ht="15.75">
+    <row r="35" spans="2:20" ht="15.75" hidden="1">
       <c r="B35" s="1" t="s">
         <v>117</v>
       </c>
@@ -3841,7 +5265,7 @@
       </c>
       <c r="T35" s="1"/>
     </row>
-    <row r="36" spans="2:20" ht="15.75">
+    <row r="36" spans="2:20" ht="15.75" hidden="1">
       <c r="B36" s="1" t="s">
         <v>3</v>
       </c>
@@ -3890,7 +5314,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="2:20" ht="15.75">
+    <row r="37" spans="2:20" ht="15.75" hidden="1">
       <c r="B37" s="1" t="s">
         <v>3</v>
       </c>
@@ -3941,7 +5365,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="2:20" ht="15.75">
+    <row r="38" spans="2:20" ht="15.75" hidden="1">
       <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
@@ -3992,7 +5416,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="2:20" ht="15.75">
+    <row r="39" spans="2:20" ht="15.75" hidden="1">
       <c r="B39" s="1" t="s">
         <v>3</v>
       </c>
@@ -4043,7 +5467,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="40" spans="2:20" ht="15.75">
+    <row r="40" spans="2:20" ht="15.75" hidden="1">
       <c r="B40" s="1" t="s">
         <v>44</v>
       </c>
@@ -4090,7 +5514,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="41" spans="2:20" ht="15.75">
+    <row r="41" spans="2:20" ht="15.75" hidden="1">
       <c r="B41" s="1" t="s">
         <v>3</v>
       </c>
@@ -4137,7 +5561,7 @@
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
     </row>
-    <row r="42" spans="2:20" ht="15.75">
+    <row r="42" spans="2:20" ht="15.75" hidden="1">
       <c r="B42" s="1" t="s">
         <v>3</v>
       </c>
@@ -4182,7 +5606,7 @@
       </c>
       <c r="T42" s="1"/>
     </row>
-    <row r="43" spans="2:20" ht="15.75">
+    <row r="43" spans="2:20" ht="15.75" hidden="1">
       <c r="B43" s="1" t="s">
         <v>60</v>
       </c>
@@ -4229,7 +5653,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="2:20" ht="15.75">
+    <row r="44" spans="2:20" ht="15.75" hidden="1">
       <c r="B44" s="1" t="s">
         <v>60</v>
       </c>
@@ -4274,7 +5698,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="2:20" ht="15.75">
+    <row r="45" spans="2:20" ht="15.75" hidden="1">
       <c r="B45" s="1" t="s">
         <v>104</v>
       </c>
@@ -4325,7 +5749,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="46" spans="2:20" ht="15.75">
+    <row r="46" spans="2:20" ht="15.75" hidden="1">
       <c r="B46" s="1" t="s">
         <v>60</v>
       </c>
@@ -4370,7 +5794,7 @@
       <c r="S46" s="1"/>
       <c r="T46" s="1"/>
     </row>
-    <row r="47" spans="2:20" ht="15.75">
+    <row r="47" spans="2:20" ht="15.75" hidden="1">
       <c r="B47" s="1" t="s">
         <v>3</v>
       </c>
@@ -4407,7 +5831,7 @@
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
     </row>
-    <row r="48" spans="2:20" ht="15.75">
+    <row r="48" spans="2:20" ht="15.75" hidden="1">
       <c r="B48" s="1" t="s">
         <v>44</v>
       </c>
@@ -4450,7 +5874,7 @@
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
     </row>
-    <row r="49" spans="2:20" ht="15.75">
+    <row r="49" spans="2:20" ht="15.75" hidden="1">
       <c r="B49" s="1" t="s">
         <v>156</v>
       </c>
@@ -4493,7 +5917,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="50" spans="2:20" ht="15.75">
+    <row r="50" spans="2:20" ht="15.75" hidden="1">
       <c r="B50" s="1" t="s">
         <v>3</v>
       </c>
@@ -4544,7 +5968,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="51" spans="2:20" ht="15.75">
+    <row r="51" spans="2:20" ht="15.75" hidden="1">
       <c r="B51" s="1" t="s">
         <v>3</v>
       </c>
@@ -4595,7 +6019,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="52" spans="2:20" ht="15.75">
+    <row r="52" spans="2:20" ht="15.75" hidden="1">
       <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
@@ -4642,7 +6066,7 @@
       </c>
       <c r="T52" s="1"/>
     </row>
-    <row r="53" spans="2:20" ht="15.75">
+    <row r="53" spans="2:20" ht="15.75" hidden="1">
       <c r="B53" s="1" t="s">
         <v>36</v>
       </c>
@@ -4687,7 +6111,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="54" spans="2:20" ht="15.75">
+    <row r="54" spans="2:20" ht="15.75" hidden="1">
       <c r="B54" s="1" t="s">
         <v>3</v>
       </c>
@@ -4738,7 +6162,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="55" spans="2:20" ht="15.75">
+    <row r="55" spans="2:20" ht="15.75" hidden="1">
       <c r="B55" s="1" t="s">
         <v>3</v>
       </c>
@@ -4783,7 +6207,7 @@
       </c>
       <c r="T55" s="1"/>
     </row>
-    <row r="56" spans="2:20" ht="15.75">
+    <row r="56" spans="2:20" ht="15.75" hidden="1">
       <c r="B56" s="1" t="s">
         <v>172</v>
       </c>
@@ -4836,7 +6260,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="57" spans="2:20" ht="15.75">
+    <row r="57" spans="2:20" ht="15.75" hidden="1">
       <c r="B57" s="1" t="s">
         <v>44</v>
       </c>
@@ -4877,7 +6301,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="2:20" ht="15.75">
+    <row r="58" spans="2:20" ht="15.75" hidden="1">
       <c r="B58" s="1" t="s">
         <v>60</v>
       </c>
@@ -4924,7 +6348,7 @@
       </c>
       <c r="T58" s="1"/>
     </row>
-    <row r="59" spans="2:20" ht="15.75">
+    <row r="59" spans="2:20" ht="15.75" hidden="1">
       <c r="B59" s="1" t="s">
         <v>3</v>
       </c>
@@ -4975,7 +6399,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" spans="2:20" ht="15.75">
+    <row r="60" spans="2:20" ht="15.75" hidden="1">
       <c r="B60" s="1" t="s">
         <v>3</v>
       </c>
@@ -5018,7 +6442,7 @@
       </c>
       <c r="T60" s="1"/>
     </row>
-    <row r="61" spans="2:20" ht="15.75">
+    <row r="61" spans="2:20" ht="15.75" hidden="1">
       <c r="B61" s="1" t="s">
         <v>45</v>
       </c>
@@ -5065,7 +6489,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="2:20" ht="15.75">
+    <row r="62" spans="2:20" ht="15.75" hidden="1">
       <c r="B62" s="1" t="s">
         <v>3</v>
       </c>
@@ -5116,7 +6540,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="63" spans="2:20" ht="15.75">
+    <row r="63" spans="2:20" ht="15.75" hidden="1">
       <c r="B63" s="1" t="s">
         <v>3</v>
       </c>
@@ -5161,7 +6585,7 @@
       <c r="S63" s="1"/>
       <c r="T63" s="1"/>
     </row>
-    <row r="64" spans="2:20" ht="15.75">
+    <row r="64" spans="2:20" ht="15.75" hidden="1">
       <c r="B64" s="1" t="s">
         <v>60</v>
       </c>
@@ -5216,7 +6640,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="65" spans="2:20" ht="15.75">
+    <row r="65" spans="2:20" ht="15.75" hidden="1">
       <c r="B65" s="1" t="s">
         <v>3</v>
       </c>
@@ -5263,7 +6687,7 @@
       </c>
       <c r="T65" s="1"/>
     </row>
-    <row r="66" spans="2:20" ht="15.75">
+    <row r="66" spans="2:20" ht="15.75" hidden="1">
       <c r="B66" s="1" t="s">
         <v>3</v>
       </c>
@@ -5308,7 +6732,7 @@
       <c r="S66" s="1"/>
       <c r="T66" s="1"/>
     </row>
-    <row r="67" spans="2:20" ht="15.75">
+    <row r="67" spans="2:20" ht="15.75" hidden="1">
       <c r="B67" s="1" t="s">
         <v>45</v>
       </c>
@@ -5361,7 +6785,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68" spans="2:20" ht="15.75">
+    <row r="68" spans="2:20" ht="15.75" hidden="1">
       <c r="B68" s="1" t="s">
         <v>3</v>
       </c>
@@ -5410,7 +6834,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="69" spans="2:20" ht="15.75">
+    <row r="69" spans="2:20" ht="15.75" hidden="1">
       <c r="B69" s="1" t="s">
         <v>16</v>
       </c>
@@ -5463,7 +6887,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="70" spans="2:20" ht="15.75">
+    <row r="70" spans="2:20" ht="15.75" hidden="1">
       <c r="B70" s="1" t="s">
         <v>3</v>
       </c>
@@ -5512,7 +6936,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="71" spans="2:20" ht="15.75">
+    <row r="71" spans="2:20" ht="15.75" hidden="1">
       <c r="B71" s="1" t="s">
         <v>3</v>
       </c>
@@ -5555,7 +6979,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="72" spans="2:20" ht="15.75">
+    <row r="72" spans="2:20" ht="15.75" hidden="1">
       <c r="B72" s="1" t="s">
         <v>3</v>
       </c>
@@ -5606,7 +7030,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="73" spans="2:20" ht="15.75">
+    <row r="73" spans="2:20" ht="15.75" hidden="1">
       <c r="B73" s="1" t="s">
         <v>208</v>
       </c>
@@ -5652,7 +7076,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="74" spans="2:20" ht="15.75">
+    <row r="74" spans="2:20" ht="15.75" hidden="1">
       <c r="B74" s="1" t="s">
         <v>3</v>
       </c>
@@ -5700,7 +7124,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75" spans="2:20" ht="15.75">
+    <row r="75" spans="2:20" ht="15.75" hidden="1">
       <c r="B75" s="1" t="s">
         <v>3</v>
       </c>
@@ -5748,7 +7172,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="76" spans="2:20" ht="15.75">
+    <row r="76" spans="2:20" ht="15.75" hidden="1">
       <c r="B76" s="1" t="s">
         <v>3</v>
       </c>
@@ -5797,7 +7221,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="77" spans="2:20" ht="15.75">
+    <row r="77" spans="2:20" ht="15.75" hidden="1">
       <c r="B77" s="1" t="s">
         <v>3</v>
       </c>
@@ -5848,7 +7272,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="78" spans="2:20" ht="15.75">
+    <row r="78" spans="2:20" ht="15.75" hidden="1">
       <c r="B78" s="1" t="s">
         <v>225</v>
       </c>
@@ -5903,7 +7327,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="2:20" ht="15.75">
+    <row r="79" spans="2:20" ht="15.75" hidden="1">
       <c r="B79" s="1" t="s">
         <v>3</v>
       </c>
@@ -5960,7 +7384,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="80" spans="2:20" ht="15.75">
+    <row r="80" spans="2:20" ht="15.75" hidden="1">
       <c r="B80" s="1" t="s">
         <v>3</v>
       </c>
@@ -6017,7 +7441,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="81" spans="2:20" ht="15.75">
+    <row r="81" spans="2:20" ht="15.75" hidden="1">
       <c r="B81" s="1" t="s">
         <v>3</v>
       </c>
@@ -6066,7 +7490,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="82" spans="2:20" ht="15.75">
+    <row r="82" spans="2:20" ht="15.75" hidden="1">
       <c r="B82" s="1" t="s">
         <v>3</v>
       </c>
@@ -6115,7 +7539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" spans="2:20" ht="15.75">
+    <row r="83" spans="2:20" ht="15.75" hidden="1">
       <c r="B83" s="1" t="s">
         <v>24</v>
       </c>
@@ -6160,7 +7584,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="84" spans="2:20" ht="15.75">
+    <row r="84" spans="2:20" ht="15.75" hidden="1">
       <c r="B84" s="1" t="s">
         <v>3</v>
       </c>
@@ -6211,7 +7635,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="85" spans="2:20" ht="15.75">
+    <row r="85" spans="2:20" ht="15.75" hidden="1">
       <c r="B85" s="1" t="s">
         <v>3</v>
       </c>
@@ -6259,7 +7683,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="86" spans="2:20" ht="15.75">
+    <row r="86" spans="2:20" ht="15.75" hidden="1">
       <c r="B86" s="1" t="s">
         <v>73</v>
       </c>
@@ -6304,7 +7728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:20" ht="15.75">
+    <row r="87" spans="2:20" ht="15.75" hidden="1">
       <c r="B87" s="1" t="s">
         <v>3</v>
       </c>
@@ -6355,7 +7779,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="88" spans="2:20" ht="15.75">
+    <row r="88" spans="2:20" ht="15.75" hidden="1">
       <c r="B88" s="1" t="s">
         <v>3</v>
       </c>
@@ -6388,7 +7812,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="89" spans="2:20" ht="15.75">
+    <row r="89" spans="2:20" ht="15.75" hidden="1">
       <c r="B89" s="1" t="s">
         <v>259</v>
       </c>
@@ -6430,7 +7854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:20" ht="15.75">
+    <row r="90" spans="2:20" ht="15.75" hidden="1">
       <c r="B90" s="1" t="s">
         <v>3</v>
       </c>
@@ -6481,7 +7905,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="91" spans="2:20" ht="15.75">
+    <row r="91" spans="2:20" ht="15.75" hidden="1">
       <c r="B91" s="1" t="s">
         <v>3</v>
       </c>
@@ -6524,7 +7948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="2:20" ht="15.75">
+    <row r="92" spans="2:20" ht="15.75" hidden="1">
       <c r="B92" s="1" t="s">
         <v>3</v>
       </c>
@@ -6572,7 +7996,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="93" spans="2:20" ht="15.75">
+    <row r="93" spans="2:20" ht="15.75" hidden="1">
       <c r="B93" s="1" t="s">
         <v>60</v>
       </c>
@@ -6617,7 +8041,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="94" spans="2:20" ht="15.75">
+    <row r="94" spans="2:20" ht="15.75" hidden="1">
       <c r="B94" s="1" t="s">
         <v>104</v>
       </c>
@@ -6662,7 +8086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:20" ht="15.75">
+    <row r="95" spans="2:20" ht="15.75" hidden="1">
       <c r="B95" s="1" t="s">
         <v>3</v>
       </c>
@@ -6713,7 +8137,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="96" spans="2:20" ht="15.75">
+    <row r="96" spans="2:20" ht="15.75" hidden="1">
       <c r="B96" s="1" t="s">
         <v>3</v>
       </c>
@@ -6758,7 +8182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:20" ht="15.75">
+    <row r="97" spans="2:20" ht="15.75" hidden="1">
       <c r="B97" s="1" t="s">
         <v>3</v>
       </c>
@@ -6800,7 +8224,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="2:20" ht="15.75">
+    <row r="98" spans="2:20" ht="15.75" hidden="1">
       <c r="B98" s="1" t="s">
         <v>3</v>
       </c>
@@ -6851,7 +8275,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="99" spans="2:20" ht="15.75">
+    <row r="99" spans="2:20" ht="15.75" hidden="1">
       <c r="B99" s="1" t="s">
         <v>3</v>
       </c>
@@ -6893,7 +8317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="2:20" ht="15.75">
+    <row r="100" spans="2:20" ht="15.75" hidden="1">
       <c r="B100" s="1" t="s">
         <v>60</v>
       </c>
@@ -6938,7 +8362,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="101" spans="2:20" ht="15.75">
+    <row r="101" spans="2:20" ht="15.75" hidden="1">
       <c r="B101" s="1" t="s">
         <v>104</v>
       </c>
@@ -6977,7 +8401,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="102" spans="2:20" ht="15.75">
+    <row r="102" spans="2:20" ht="15.75" hidden="1">
       <c r="B102" s="1" t="s">
         <v>3</v>
       </c>
@@ -7025,7 +8449,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="2:20" ht="15.75">
+    <row r="103" spans="2:20" ht="15.75" hidden="1">
       <c r="B103" s="1" t="s">
         <v>3</v>
       </c>
@@ -7064,7 +8488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="2:20" ht="15.75">
+    <row r="104" spans="2:20" ht="15.75" hidden="1">
       <c r="B104" s="1" t="s">
         <v>3</v>
       </c>
@@ -7093,7 +8517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:20" ht="15.75">
+    <row r="105" spans="2:20" ht="15.75" hidden="1">
       <c r="B105" s="1" t="s">
         <v>3</v>
       </c>
@@ -7122,7 +8546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="2:20" ht="15.75">
+    <row r="106" spans="2:20" ht="15.75" hidden="1">
       <c r="B106" s="1" t="s">
         <v>259</v>
       </c>
@@ -7167,7 +8591,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="107" spans="2:20" ht="15.75">
+    <row r="107" spans="2:20" ht="15.75" hidden="1">
       <c r="B107" s="1" t="s">
         <v>3</v>
       </c>
@@ -7212,7 +8636,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="108" spans="2:20" ht="15.75">
+    <row r="108" spans="2:20" ht="15.75" hidden="1">
       <c r="B108" s="1" t="s">
         <v>3</v>
       </c>
@@ -7261,7 +8685,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="109" spans="2:20" ht="15.75">
+    <row r="109" spans="2:20" ht="15.75" hidden="1">
       <c r="B109" s="1" t="s">
         <v>3</v>
       </c>
@@ -7308,7 +8732,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="110" spans="2:20" ht="15.75">
+    <row r="110" spans="2:20" ht="15.75" hidden="1">
       <c r="B110" s="1" t="s">
         <v>3</v>
       </c>
@@ -7356,7 +8780,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="111" spans="2:20" ht="15.75">
+    <row r="111" spans="2:20" ht="15.75" hidden="1">
       <c r="B111" s="1" t="s">
         <v>3</v>
       </c>
@@ -7401,7 +8825,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="112" spans="2:20" ht="15.75">
+    <row r="112" spans="2:20" ht="15.75" hidden="1">
       <c r="B112" s="1" t="s">
         <v>3</v>
       </c>
@@ -7452,7 +8876,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="15.75">
+    <row r="113" spans="1:20" ht="15.75" hidden="1">
       <c r="B113" s="1" t="s">
         <v>45</v>
       </c>
@@ -7503,7 +8927,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="15.75">
+    <row r="114" spans="1:20" ht="15.75" hidden="1">
       <c r="B114" s="1" t="s">
         <v>3</v>
       </c>
@@ -7551,7 +8975,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="15.75">
+    <row r="115" spans="1:20" ht="15.75" hidden="1">
       <c r="B115" s="1" t="s">
         <v>334</v>
       </c>
@@ -7575,7 +8999,7 @@
       </c>
       <c r="K115" s="1"/>
     </row>
-    <row r="116" spans="1:20" ht="15.75">
+    <row r="116" spans="1:20" ht="15.75" hidden="1">
       <c r="B116" s="1" t="s">
         <v>3</v>
       </c>
@@ -7604,7 +9028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="15.75">
+    <row r="117" spans="1:20" ht="15.75" hidden="1">
       <c r="B117" s="1" t="s">
         <v>3</v>
       </c>
@@ -7652,7 +9076,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="15.75">
+    <row r="118" spans="1:20" ht="15.75" hidden="1">
       <c r="B118" s="1" t="s">
         <v>3</v>
       </c>
@@ -7688,7 +9112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="15.75">
+    <row r="119" spans="1:20" ht="15.75" hidden="1">
       <c r="B119" s="1" t="s">
         <v>3</v>
       </c>
@@ -7727,7 +9151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="15.75">
+    <row r="120" spans="1:20" ht="15.75" hidden="1">
       <c r="B120" s="1" t="s">
         <v>3</v>
       </c>
@@ -7772,7 +9196,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="15.75">
+    <row r="121" spans="1:20" ht="15.75" hidden="1">
       <c r="B121" s="1" t="s">
         <v>60</v>
       </c>
@@ -7817,7 +9241,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="15.75">
+    <row r="122" spans="1:20" ht="15.75" hidden="1">
       <c r="B122" s="1" t="s">
         <v>60</v>
       </c>
@@ -7859,7 +9283,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="15.75">
+    <row r="123" spans="1:20" ht="15.75" hidden="1">
       <c r="B123" s="1" t="s">
         <v>3</v>
       </c>
@@ -7907,7 +9331,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="15.75">
+    <row r="124" spans="1:20" ht="15.75" hidden="1">
       <c r="B124" s="1" t="s">
         <v>3</v>
       </c>
@@ -7958,7 +9382,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="15.75">
+    <row r="125" spans="1:20" ht="15.75" hidden="1">
       <c r="B125" s="1" t="s">
         <v>3</v>
       </c>
@@ -7975,7 +9399,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="15.75">
+    <row r="126" spans="1:20" ht="15.75" hidden="1">
       <c r="B126" s="1" t="s">
         <v>3</v>
       </c>
@@ -8026,7 +9450,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="16.5" thickBot="1">
+    <row r="127" spans="1:20" ht="16.5" hidden="1">
       <c r="B127" s="1" t="s">
         <v>3</v>
       </c>
@@ -8065,7 +9489,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="39" thickBot="1">
+    <row r="128" spans="1:20" ht="39" hidden="1" thickBot="1">
       <c r="A128" s="18" t="s">
         <v>360</v>
       </c>
@@ -8733,8 +10157,11 @@
       <c r="J144" t="s">
         <v>367</v>
       </c>
+      <c r="K144" t="s">
+        <v>402</v>
+      </c>
       <c r="L144" t="s">
-        <v>402</v>
+        <v>7</v>
       </c>
       <c r="M144">
         <v>1</v>
@@ -8746,9 +10173,392 @@
         <v>374</v>
       </c>
     </row>
+    <row r="145" spans="2:20" ht="15.75">
+      <c r="B145" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C145" s="11">
+        <v>46069</v>
+      </c>
+      <c r="D145" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E145" s="7">
+        <v>46069</v>
+      </c>
+      <c r="F145" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G145" t="s">
+        <v>12</v>
+      </c>
+      <c r="H145" t="s">
+        <v>9</v>
+      </c>
+      <c r="I145" t="s">
+        <v>9</v>
+      </c>
+      <c r="J145" t="s">
+        <v>21</v>
+      </c>
+      <c r="K145" t="s">
+        <v>400</v>
+      </c>
+      <c r="L145" t="s">
+        <v>404</v>
+      </c>
+      <c r="M145">
+        <v>1</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="P145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="2:20" ht="15.75">
+      <c r="B146" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="C146" s="11">
+        <v>46071</v>
+      </c>
+      <c r="E146" s="7">
+        <v>46071</v>
+      </c>
+      <c r="F146" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G146" t="s">
+        <v>111</v>
+      </c>
+      <c r="H146" t="s">
+        <v>112</v>
+      </c>
+      <c r="I146" t="s">
+        <v>406</v>
+      </c>
+      <c r="J146" t="s">
+        <v>407</v>
+      </c>
+      <c r="K146" t="s">
+        <v>408</v>
+      </c>
+      <c r="L146" t="s">
+        <v>409</v>
+      </c>
+      <c r="M146">
+        <v>1</v>
+      </c>
+      <c r="N146">
+        <v>1</v>
+      </c>
+      <c r="P146">
+        <v>1</v>
+      </c>
+      <c r="S146" t="s">
+        <v>410</v>
+      </c>
+      <c r="T146" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="147" spans="2:20" ht="15.75">
+      <c r="B147" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="C147" s="11">
+        <v>46071</v>
+      </c>
+      <c r="E147" s="7">
+        <v>46072</v>
+      </c>
+      <c r="F147" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G147" t="s">
+        <v>74</v>
+      </c>
+      <c r="H147" t="s">
+        <v>89</v>
+      </c>
+      <c r="I147" t="s">
+        <v>89</v>
+      </c>
+      <c r="J147" t="s">
+        <v>412</v>
+      </c>
+      <c r="K147" t="s">
+        <v>127</v>
+      </c>
+      <c r="L147" t="s">
+        <v>21</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+      <c r="N147">
+        <v>1</v>
+      </c>
+      <c r="P147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="2:20" ht="15.75">
+      <c r="B148" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="11">
+        <v>46074</v>
+      </c>
+      <c r="D148" t="s">
+        <v>21</v>
+      </c>
+      <c r="E148" s="7">
+        <v>46074</v>
+      </c>
+      <c r="F148" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G148" t="s">
+        <v>74</v>
+      </c>
+      <c r="I148" t="s">
+        <v>413</v>
+      </c>
+      <c r="J148" t="s">
+        <v>21</v>
+      </c>
+      <c r="K148" t="s">
+        <v>400</v>
+      </c>
+      <c r="L148" t="s">
+        <v>21</v>
+      </c>
+      <c r="M148">
+        <v>1</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="P148">
+        <v>1</v>
+      </c>
+      <c r="T148" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="149" spans="2:20" ht="15.75">
+      <c r="B149" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C149" s="11">
+        <v>46076</v>
+      </c>
+      <c r="D149" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E149" s="7">
+        <v>46076</v>
+      </c>
+      <c r="F149" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G149" t="s">
+        <v>74</v>
+      </c>
+      <c r="H149" t="s">
+        <v>378</v>
+      </c>
+      <c r="I149" t="s">
+        <v>378</v>
+      </c>
+      <c r="J149" t="s">
+        <v>414</v>
+      </c>
+      <c r="K149" t="s">
+        <v>415</v>
+      </c>
+      <c r="L149" t="s">
+        <v>7</v>
+      </c>
+      <c r="M149">
+        <v>2</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>2</v>
+      </c>
+      <c r="T149" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="150" spans="2:20" ht="15.75">
+      <c r="B150" s="22" t="s">
+        <v>418</v>
+      </c>
+      <c r="C150" s="11">
+        <v>46077</v>
+      </c>
+      <c r="E150" s="7">
+        <v>46077</v>
+      </c>
+      <c r="F150" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="G150" t="s">
+        <v>33</v>
+      </c>
+      <c r="H150" t="s">
+        <v>157</v>
+      </c>
+      <c r="M150">
+        <v>14</v>
+      </c>
+      <c r="N150">
+        <v>6</v>
+      </c>
+      <c r="O150">
+        <v>8</v>
+      </c>
+      <c r="P150">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="2:20" ht="15.75">
+      <c r="B151" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="C151" s="11">
+        <v>46072</v>
+      </c>
+      <c r="D151" s="15">
+        <v>0.3125</v>
+      </c>
+      <c r="E151" s="7">
+        <v>46072</v>
+      </c>
+      <c r="F151" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G151" t="s">
+        <v>141</v>
+      </c>
+      <c r="H151" t="s">
+        <v>210</v>
+      </c>
+      <c r="I151" t="s">
+        <v>210</v>
+      </c>
+      <c r="J151" t="s">
+        <v>412</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>1</v>
+      </c>
+      <c r="P151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="2:20" ht="15.75">
+      <c r="B152" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C152" s="11">
+        <v>46079</v>
+      </c>
+      <c r="D152" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="E152" s="7">
+        <v>46080</v>
+      </c>
+      <c r="F152" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G152" t="s">
+        <v>12</v>
+      </c>
+      <c r="H152" t="s">
+        <v>176</v>
+      </c>
+      <c r="I152" t="s">
+        <v>303</v>
+      </c>
+      <c r="J152" t="s">
+        <v>367</v>
+      </c>
+      <c r="K152" t="s">
+        <v>421</v>
+      </c>
+      <c r="L152" t="s">
+        <v>7</v>
+      </c>
+      <c r="M152">
+        <v>2</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>422</v>
+      </c>
+      <c r="T152" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="153" spans="2:20" ht="15.75">
+      <c r="B153" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="C153" s="11">
+        <v>46054</v>
+      </c>
+      <c r="E153" s="6">
+        <v>46054</v>
+      </c>
+      <c r="F153" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="G153" t="s">
+        <v>12</v>
+      </c>
+      <c r="I153" t="s">
+        <v>428</v>
+      </c>
+      <c r="J153" t="s">
+        <v>429</v>
+      </c>
+      <c r="M153">
+        <f>SUM(M130:M152)</f>
+        <v>44</v>
+      </c>
+      <c r="N153">
+        <f>SUM(N130:N152)</f>
+        <v>17</v>
+      </c>
+      <c r="O153">
+        <f>SUM(O130:O152)</f>
+        <v>10</v>
+      </c>
+      <c r="P153">
+        <f>SUM(P130:P152)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="2:20">
+      <c r="Q154" t="s">
+        <v>427</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:T128">
-    <filterColumn colId="10"/>
+    <filterColumn colId="4">
+      <dynamicFilter type="thisYear" val="46023" maxVal="46388"/>
+    </filterColumn>
   </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="I1:Q1"/>
@@ -8756,4 +10566,1187 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A3:B9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2">
+      <c r="A3" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B9" s="14">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A3:B19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2">
+      <c r="A3" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="25">
+        <v>46023</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="25">
+        <v>46032</v>
+      </c>
+      <c r="B6" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="25">
+        <v>46038</v>
+      </c>
+      <c r="B7" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="25">
+        <v>46050</v>
+      </c>
+      <c r="B8" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="25">
+        <v>46054</v>
+      </c>
+      <c r="B9" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="25">
+        <v>46058</v>
+      </c>
+      <c r="B10" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="25">
+        <v>46065</v>
+      </c>
+      <c r="B11" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="25">
+        <v>46069</v>
+      </c>
+      <c r="B12" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="25">
+        <v>46071</v>
+      </c>
+      <c r="B13" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="25">
+        <v>46072</v>
+      </c>
+      <c r="B14" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="25">
+        <v>46074</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="25">
+        <v>46076</v>
+      </c>
+      <c r="B16" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="25">
+        <v>46077</v>
+      </c>
+      <c r="B17" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="25">
+        <v>46079</v>
+      </c>
+      <c r="B18" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B19" s="14">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:T23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="18.75">
+      <c r="A1" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="T1" s="5"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75">
+      <c r="A2" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>46023</v>
+      </c>
+      <c r="C2" s="15">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D2" s="7">
+        <v>46023</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" t="s">
+        <v>367</v>
+      </c>
+      <c r="K2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="P2" t="s">
+        <v>376</v>
+      </c>
+      <c r="R2" t="s">
+        <v>377</v>
+      </c>
+      <c r="S2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15.75">
+      <c r="A3" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="11">
+        <v>46032</v>
+      </c>
+      <c r="D3" s="7">
+        <v>46032</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" t="s">
+        <v>378</v>
+      </c>
+      <c r="H3" t="s">
+        <v>379</v>
+      </c>
+      <c r="I3" t="s">
+        <v>381</v>
+      </c>
+      <c r="J3" t="s">
+        <v>388</v>
+      </c>
+      <c r="K3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
+        <v>382</v>
+      </c>
+      <c r="S3" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15.75">
+      <c r="A4" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C4" s="15">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D4" s="7">
+        <v>46050</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" t="s">
+        <v>252</v>
+      </c>
+      <c r="H4" t="s">
+        <v>384</v>
+      </c>
+      <c r="I4" t="s">
+        <v>367</v>
+      </c>
+      <c r="J4" t="s">
+        <v>385</v>
+      </c>
+      <c r="K4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="P4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15.75">
+      <c r="A5" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C5" s="15">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D5" s="7">
+        <v>46050</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H5" t="s">
+        <v>384</v>
+      </c>
+      <c r="I5" t="s">
+        <v>367</v>
+      </c>
+      <c r="J5" t="s">
+        <v>385</v>
+      </c>
+      <c r="K5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="P5" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15.75">
+      <c r="A6" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="B6" s="11">
+        <v>46038</v>
+      </c>
+      <c r="C6" s="15">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D6" s="7">
+        <v>46038</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" t="s">
+        <v>387</v>
+      </c>
+      <c r="I6" t="s">
+        <v>391</v>
+      </c>
+      <c r="J6" t="s">
+        <v>389</v>
+      </c>
+      <c r="K6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>2</v>
+      </c>
+      <c r="R6" t="s">
+        <v>390</v>
+      </c>
+      <c r="S6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.75">
+      <c r="A7" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C7" s="15">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D7" s="7">
+        <v>46050</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" t="s">
+        <v>252</v>
+      </c>
+      <c r="H7" t="s">
+        <v>393</v>
+      </c>
+      <c r="I7" t="s">
+        <v>367</v>
+      </c>
+      <c r="J7" t="s">
+        <v>385</v>
+      </c>
+      <c r="K7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="P7" t="s">
+        <v>386</v>
+      </c>
+      <c r="S7" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15.75">
+      <c r="A8" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="11">
+        <v>46050</v>
+      </c>
+      <c r="C8" s="15">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>46050</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" t="s">
+        <v>252</v>
+      </c>
+      <c r="H8" t="s">
+        <v>393</v>
+      </c>
+      <c r="I8" t="s">
+        <v>367</v>
+      </c>
+      <c r="J8" t="s">
+        <v>385</v>
+      </c>
+      <c r="K8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="P8" t="s">
+        <v>386</v>
+      </c>
+      <c r="S8" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15.75">
+      <c r="A9" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="11">
+        <v>46058</v>
+      </c>
+      <c r="C9" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D9" s="7">
+        <v>46058</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H9" t="s">
+        <v>395</v>
+      </c>
+      <c r="I9" t="s">
+        <v>399</v>
+      </c>
+      <c r="J9" t="s">
+        <v>396</v>
+      </c>
+      <c r="K9" t="s">
+        <v>7</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15.75">
+      <c r="A10" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="11">
+        <v>46054</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="I10" t="s">
+        <v>399</v>
+      </c>
+      <c r="J10" t="s">
+        <v>400</v>
+      </c>
+      <c r="K10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="S10" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.75">
+      <c r="A11" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="11">
+        <v>46054</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="I11" t="s">
+        <v>260</v>
+      </c>
+      <c r="J11" t="s">
+        <v>401</v>
+      </c>
+      <c r="K11" t="s">
+        <v>261</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="S11" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15.75">
+      <c r="A12" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46054</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" t="s">
+        <v>260</v>
+      </c>
+      <c r="K12" t="s">
+        <v>261</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="S12" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15.75">
+      <c r="A13" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="11">
+        <v>46065</v>
+      </c>
+      <c r="C13" s="15">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D13" s="7">
+        <v>46066</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" t="s">
+        <v>252</v>
+      </c>
+      <c r="H13" t="s">
+        <v>393</v>
+      </c>
+      <c r="I13" t="s">
+        <v>367</v>
+      </c>
+      <c r="J13" t="s">
+        <v>402</v>
+      </c>
+      <c r="K13" t="s">
+        <v>7</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="P13" t="s">
+        <v>403</v>
+      </c>
+      <c r="S13" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15.75">
+      <c r="A14" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="11">
+        <v>46065</v>
+      </c>
+      <c r="C14" s="15">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D14" s="7">
+        <v>46066</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" t="s">
+        <v>252</v>
+      </c>
+      <c r="H14" t="s">
+        <v>393</v>
+      </c>
+      <c r="I14" t="s">
+        <v>367</v>
+      </c>
+      <c r="J14" t="s">
+        <v>402</v>
+      </c>
+      <c r="K14" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="P14" t="s">
+        <v>403</v>
+      </c>
+      <c r="S14" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15.75">
+      <c r="A15" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <v>46069</v>
+      </c>
+      <c r="C15" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D15" s="7">
+        <v>46069</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>400</v>
+      </c>
+      <c r="K15" t="s">
+        <v>404</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15.75">
+      <c r="A16" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="B16" s="11">
+        <v>46071</v>
+      </c>
+      <c r="D16" s="7">
+        <v>46071</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H16" t="s">
+        <v>406</v>
+      </c>
+      <c r="I16" t="s">
+        <v>407</v>
+      </c>
+      <c r="J16" t="s">
+        <v>408</v>
+      </c>
+      <c r="K16" t="s">
+        <v>409</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="R16" t="s">
+        <v>410</v>
+      </c>
+      <c r="S16" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15.75">
+      <c r="A17" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="B17" s="11">
+        <v>46071</v>
+      </c>
+      <c r="D17" s="7">
+        <v>46072</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" t="s">
+        <v>412</v>
+      </c>
+      <c r="J17" t="s">
+        <v>127</v>
+      </c>
+      <c r="K17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15.75">
+      <c r="A18" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="11">
+        <v>46074</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="7">
+        <v>46074</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>413</v>
+      </c>
+      <c r="I18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>400</v>
+      </c>
+      <c r="K18" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="S18" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15.75">
+      <c r="A19" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="11">
+        <v>46076</v>
+      </c>
+      <c r="C19" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D19" s="7">
+        <v>46076</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s">
+        <v>378</v>
+      </c>
+      <c r="H19" t="s">
+        <v>378</v>
+      </c>
+      <c r="I19" t="s">
+        <v>414</v>
+      </c>
+      <c r="J19" t="s">
+        <v>415</v>
+      </c>
+      <c r="K19" t="s">
+        <v>7</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="S19" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15.75">
+      <c r="A20" s="22" t="s">
+        <v>418</v>
+      </c>
+      <c r="B20" s="11">
+        <v>46077</v>
+      </c>
+      <c r="D20" s="7">
+        <v>46077</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" t="s">
+        <v>157</v>
+      </c>
+      <c r="L20">
+        <v>14</v>
+      </c>
+      <c r="M20">
+        <v>6</v>
+      </c>
+      <c r="N20">
+        <v>8</v>
+      </c>
+      <c r="O20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15.75">
+      <c r="A21" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="B21" s="11">
+        <v>46072</v>
+      </c>
+      <c r="C21" s="15">
+        <v>0.3125</v>
+      </c>
+      <c r="D21" s="7">
+        <v>46072</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" t="s">
+        <v>210</v>
+      </c>
+      <c r="H21" t="s">
+        <v>210</v>
+      </c>
+      <c r="I21" t="s">
+        <v>412</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15.75">
+      <c r="A22" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="11">
+        <v>46079</v>
+      </c>
+      <c r="C22" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="D22" s="7">
+        <v>46080</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>176</v>
+      </c>
+      <c r="H22" t="s">
+        <v>303</v>
+      </c>
+      <c r="I22" t="s">
+        <v>367</v>
+      </c>
+      <c r="J22" t="s">
+        <v>421</v>
+      </c>
+      <c r="K22" t="s">
+        <v>7</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="P22" t="s">
+        <v>422</v>
+      </c>
+      <c r="S22" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15.75">
+      <c r="A23" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="P23" t="s">
+        <v>427</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>